--- a/Test-case.xlsx
+++ b/Test-case.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="8676" activeTab="4"/>
+    <workbookView windowWidth="23040" windowHeight="8280" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
     <sheet name="Traceability" sheetId="2" r:id="rId2"/>
-    <sheet name="TestCases" sheetId="3" r:id="rId3"/>
+    <sheet name="TestCases" sheetId="6" r:id="rId3"/>
     <sheet name="Execution" sheetId="4" r:id="rId4"/>
     <sheet name="Bugs" sheetId="5" r:id="rId5"/>
   </sheets>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="419">
   <si>
     <t>Req ID</t>
   </si>
@@ -306,487 +306,919 @@
     <t>TC-SORT-04</t>
   </si>
   <si>
-    <t>Test Case ID</t>
-  </si>
-  <si>
-    <t>Technique (EP/BVA/DT/UC)</t>
+    <t>Mã TC</t>
+  </si>
+  <si>
+    <t>Tên test case</t>
+  </si>
+  <si>
+    <t>Đăng nhập với tài khoản hợp lệ hoạt động bình thường</t>
+  </si>
+  <si>
+    <t>Yêu cầu / Kỹ thuật</t>
+  </si>
+  <si>
+    <t>FR-01.1 — Phân vùng tương đương (EP) - Lớp EC1 (Hợp lệ)</t>
+  </si>
+  <si>
+    <t>Tiền điều kiện</t>
+  </si>
+  <si>
+    <t>Người dùng đã mở trình duyệt và đang ở trang đăng nhập https://www.saucedemo.com/</t>
+  </si>
+  <si>
+    <t>Dữ liệu kiểm thử</t>
+  </si>
+  <si>
+    <t>Username: standard_user | Password: secret_sauce</t>
+  </si>
+  <si>
+    <t>Bước</t>
+  </si>
+  <si>
+    <t>Thao tác</t>
+  </si>
+  <si>
+    <t>Kết quả mong đợi</t>
+  </si>
+  <si>
+    <t>Quan sát trạng thái ban đầu tại trang đăng nhập</t>
+  </si>
+  <si>
+    <t>Hiển thị đầy đủ ô nhập Username, Password và nút «Login»</t>
+  </si>
+  <si>
+    <t>Nhập «standard_user» vào ô Username</t>
+  </si>
+  <si>
+    <t>Ô Username hiển thị chuỗi «standard_user»</t>
+  </si>
+  <si>
+    <t>Nhập «secret_sauce» vào ô Password</t>
+  </si>
+  <si>
+    <t>Ô Password hiển thị các ký tự được che ẩn</t>
+  </si>
+  <si>
+    <t>Bấm nút «Login»</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công và chuyển hướng đến trang danh sách sản phẩm inventory.html</t>
+  </si>
+  <si>
+    <t>Đăng nhập với tài khoản tồn tại nhưng bị khóa</t>
+  </si>
+  <si>
+    <t>FR-01.4 — Phân vùng tương đương (EP) - Lớp EC2 (Không hợp lệ)</t>
+  </si>
+  <si>
+    <t>Người dùng đang ở trang đăng nhập https://www.saucedemo.com/</t>
+  </si>
+  <si>
+    <t>Username: locked_out_user | Password: secret_sauce</t>
+  </si>
+  <si>
+    <t>Nhập «locked_out_user» vào ô Username</t>
+  </si>
+  <si>
+    <t>Ô Username hiển thị chuỗi «locked_out_user»</t>
+  </si>
+  <si>
+    <t>Không chuyển trang; hiển thị thông báo lỗi: «Epic sadface: Sorry, this user has been locked out.»</t>
+  </si>
+  <si>
+    <t>TC-LOGIN-DT-01</t>
+  </si>
+  <si>
+    <t>Để trống Username khi đăng nhập</t>
+  </si>
+  <si>
+    <t>FR-01.2 — Bảng quyết định (DT - Quy tắc R1) &amp; Phân vùng tương đương (EC3)</t>
+  </si>
+  <si>
+    <t>Username: "" (rỗng) | Password: secret_sauce</t>
+  </si>
+  <si>
+    <t>Để trống ô Username</t>
+  </si>
+  <si>
+    <t>Ô Username giữ trạng thái trống</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi: «Epic sadface: Username is required»</t>
+  </si>
+  <si>
+    <t>TC-LOGIN-DT-02</t>
+  </si>
+  <si>
+    <t>Để trống Password khi đăng nhập</t>
+  </si>
+  <si>
+    <t>FR-01.2 — Bảng quyết định (DT - Quy tắc R2)</t>
+  </si>
+  <si>
+    <t>Username: standard_user | Password: "" (rỗng)</t>
+  </si>
+  <si>
+    <t>Để trống ô Password</t>
+  </si>
+  <si>
+    <t>Ô Password giữ trạng thái trống</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi: «Epic sadface: Password is required»</t>
+  </si>
+  <si>
+    <t>Đăng nhập sai thông tin (sai Mật khẩu hoặc tài khoản không tồn tại)</t>
+  </si>
+  <si>
+    <t>FR-01.3 — Phân vùng tương đương (EP - EC4/EC5) &amp; Bảng quyết định (DT - Quy tắc R3)</t>
+  </si>
+  <si>
+    <t>Username: standard_user | Password: wrong_password</t>
+  </si>
+  <si>
+    <t>Nhập «wrong_password» vào ô Password</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi: «Epic sadface: Username and password do not match any user in this service»</t>
+  </si>
+  <si>
+    <t>Đo thời gian phản hồi tải trang sản phẩm sau khi đăng nhập</t>
+  </si>
+  <si>
+    <t>NFR-01.1 — Kiểm thử hiệu năng (Performance Testing)</t>
+  </si>
+  <si>
+    <t>Người dùng đang ở trang đăng nhập https://www.saucedemo.com/; bộ đo thời gian đã sẵn sàng</t>
+  </si>
+  <si>
+    <t>Username: performance_glitch_user | Password: secret_sauce</t>
+  </si>
+  <si>
+    <t>Nhập «performance_glitch_user» vào ô Username</t>
+  </si>
+  <si>
+    <t>Ô Username hiển thị chuỗi «performance_glitch_user»</t>
+  </si>
+  <si>
+    <t>Bấm nút «Login» và bắt đầu bấm giờ đo thời gian phản hồi cho đến khi trang inventory.html tải hoàn tất</t>
+  </si>
+  <si>
+    <t>Trang inventory.html hiển thị đầy đủ danh sách sản phẩm trong thời gian tối đa &lt;= 3 giây (3000 ms)</t>
+  </si>
+  <si>
+    <t>TC-CART-B1</t>
+  </si>
+  <si>
+    <t>Kiểm tra giá trị biên dưới ngoài miền (giá trị -1)</t>
+  </si>
+  <si>
+    <t>FR-02 — BVA, giá trị min - 1 = -1 (ngoài miền giá trị)</t>
+  </si>
+  <si>
+    <t>Không có — giá trị -1 không thể tạo bằng thao tác giao diện</t>
+  </si>
+  <si>
+    <t>Không có</t>
+  </si>
+  <si>
+    <t>Quan sát inventory.html và cart.html: xác nhận không tồn tại trường nhập số lượng, mỗi sản phẩm chỉ có nút «Add to cart» / «Remove»</t>
+  </si>
+  <si>
+    <t>Xác nhận không có thao tác nào tạo được giỏ có -1 sản phẩm</t>
+  </si>
+  <si>
+    <t>Ghi nhận kết quả phân tích vào báo cáo kiểm thử</t>
+  </si>
+  <si>
+    <t>TC-CART-B1 được đánh dấu «không áp dụng» kèm lý do tường minh</t>
+  </si>
+  <si>
+    <t>TC-CART-B2</t>
+  </si>
+  <si>
+    <t>Kiểm tra giá trị biên dưới min = 0 — giỏ hàng trống</t>
+  </si>
+  <si>
+    <t>FR-02 (FR-02.4, FR-02.5) — BVA, giá trị min = 0</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập bằng standard_user; chưa thêm sản phẩm nào vào giỏ</t>
+  </si>
+  <si>
+    <t>Tài khoản standard_user / mật khẩu secret_sauce</t>
+  </si>
+  <si>
+    <t>Truy cập https://www.saucedemo.com, đăng nhập bằng standard_user / secret_sauce</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công, mở được inventory.html</t>
+  </si>
+  <si>
+    <t>Không thêm sản phẩm nào; bấm vào biểu tượng giỏ hàng</t>
+  </si>
+  <si>
+    <t>Mở được cart.html</t>
+  </si>
+  <si>
+    <t>Quan sát badge trên biểu tượng giỏ và danh sách sản phẩm trong giỏ</t>
+  </si>
+  <si>
+    <t>Badge không hiển thị; danh sách giỏ trống (0 hàng); các nút chức năng hiển thị bình thường</t>
+  </si>
+  <si>
+    <t>TC-CART-B3</t>
+  </si>
+  <si>
+    <t>Kiểm tra giá trị biên min + 1 = 1 — thêm đúng một sản phẩm</t>
+  </si>
+  <si>
+    <t>FR-02 (FR-02.2, FR-02.3, FR-02.6) — BVA, giá trị min + 1 = 1</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập bằng standard_user; giỏ hàng đang trống</t>
+  </si>
+  <si>
+    <t>Sauce Labs Backpack — $29.99</t>
+  </si>
+  <si>
+    <t>Trên inventory.html, bấm «Add to cart» tại thẻ Sauce Labs Backpack</t>
+  </si>
+  <si>
+    <t>Nút chuyển thành «Remove»</t>
+  </si>
+  <si>
+    <t>Quan sát badge trên biểu tượng giỏ hàng</t>
+  </si>
+  <si>
+    <t>Badge hiển thị «1»</t>
+  </si>
+  <si>
+    <t>Bấm biểu tượng giỏ để mở cart.html</t>
+  </si>
+  <si>
+    <t>Giỏ có đúng 1 hàng: tên «Sauce Labs Backpack», mô tả đầy đủ, giá $29.99</t>
+  </si>
+  <si>
+    <t>TC-CART-B4</t>
+  </si>
+  <si>
+    <t>Kiểm tra giá trị biên max - 1 = 5 — giỏ có 5 sản phẩm</t>
+  </si>
+  <si>
+    <t>FR-02 (FR-02.3, FR-02.5, FR-02.6) — BVA, giá trị max - 1 = 5</t>
+  </si>
+  <si>
+    <t>5 sản phẩm: Sauce Labs Backpack (29.99),SauceLabsBikeLight(9.99), Sauce Labs Bolt T-Shirt (15.99),SauceLabsFleeceJacket(49.99), Sauce Labs Onesie ($7.99)</t>
+  </si>
+  <si>
+    <t>Đăng nhập bằng standard_user / secret_sauce</t>
+  </si>
+  <si>
+    <t>inventory.html hiển thị 6 sản phẩm</t>
+  </si>
+  <si>
+    <t>Thêm lần lượt 5 sản phẩm nêu trên (không thêm Test.allTheThings() T-Shirt (Red))</t>
+  </si>
+  <si>
+    <t>Sau mỗi lần thêm, badge tăng đúng 1: 1 → 2 → 3 → 4 → 5</t>
+  </si>
+  <si>
+    <t>Quan sát badge sau khi thêm xong</t>
+  </si>
+  <si>
+    <t>Badge hiển thị «5»</t>
+  </si>
+  <si>
+    <t>Mở cart.html</t>
+  </si>
+  <si>
+    <t>Giỏ có đúng 5 hàng, tên và giá khớp từng sản phẩm; không có Test.allTheThings() T-Shirt (Red)</t>
+  </si>
+  <si>
+    <t>TC-CART-B5</t>
+  </si>
+  <si>
+    <t>Kiểm tra giá trị biên max = 6 — giỏ đầy 6 sản phẩm</t>
+  </si>
+  <si>
+    <t>FR-02 (FR-02.3, FR-02.6) — BVA, giá trị max = 6</t>
+  </si>
+  <si>
+    <t>Cả 6 sản phẩm của cửa hàng: Sauce Labs Backpack (29.99),SauceLabsBikeLight(9.99), Sauce Labs Bolt T-Shirt (15.99),SauceLabsFleeceJacket(49.99), Sauce Labs Onesie (7.99),Test.allTheThings()T-Shirt(Red)(15.99)</t>
+  </si>
+  <si>
+    <t>Thêm lần lượt cả 6 sản phẩm</t>
+  </si>
+  <si>
+    <t>Badge tăng dần 1 → 2 → … → 6; cả 6 nút chuyển thành «Remove»</t>
+  </si>
+  <si>
+    <t>Badge hiển thị «6» — giá trị lớn nhất mà giao diện cho phép</t>
+  </si>
+  <si>
+    <t>Giỏ có đúng 6 hàng, tên và giá khớp; các nút «Remove» hiển thị trong giỏ</t>
+  </si>
+  <si>
+    <t>TC-CART-UC1</t>
+  </si>
+  <si>
+    <t>Mua sắm trọn vẹn với giỏ hàng (luồng chính)</t>
+  </si>
+  <si>
+    <t>FR-02 — Kiểm thử dựa trên ca sử dụng, luồng chính</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập thành công bằng tài khoản standard_user; giỏ hàng đang trống</t>
+  </si>
+  <si>
+    <t>Sauce Labs Backpack (29.99);SauceLabsBikeLight(9.99); tài khoản standard_user / secret_sauce</t>
+  </si>
+  <si>
+    <t>Quan sát trạng thái ban đầu tại inventory.html sau khi đăng nhập</t>
+  </si>
+  <si>
+    <t>Hiển thị 6 sản phẩm; badge ẩn (giỏ trống); nút Backpack là «Add to cart»</t>
+  </si>
+  <si>
+    <t>Bấm «Add to cart» tại thẻ Sauce Labs Backpack</t>
+  </si>
+  <si>
+    <t>Nút chuyển thành «Remove»; badge hiển thị «1»</t>
+  </si>
+  <si>
+    <t>Bấm «Add to cart» tại thẻ Sauce Labs Bike Light</t>
+  </si>
+  <si>
+    <t>Nút chuyển thành «Remove»; badge hiển thị «2»</t>
+  </si>
+  <si>
+    <t>Bấm biểu tượng giỏ hàng</t>
+  </si>
+  <si>
+    <t>Mở cart.html với đúng 2 hàng, tên và giá khớp sản phẩm đã thêm</t>
+  </si>
+  <si>
+    <t>Bấm «Remove» của Sauce Labs Backpack trong giỏ</t>
+  </si>
+  <si>
+    <t>Hàng Backpack biến mất; giỏ còn 1 hàng Bike Light; badge hiển thị «1»</t>
+  </si>
+  <si>
+    <t>Bấm «Continue Shopping»</t>
+  </si>
+  <si>
+    <t>Quay về inventory.html; nút Bike Light vẫn là «Remove»; badge giữ «1»</t>
+  </si>
+  <si>
+    <t>TC-CART-UC3</t>
+  </si>
+  <si>
+    <t>Xóa sản phẩm ngay trên trang danh sách sản phẩm</t>
+  </si>
+  <si>
+    <t>FR-02 (FR-02.2, FR-02.5) — Kiểm thử dựa trên ca sử dụng, luồng A2 «Xóa trên trang sản phẩm»</t>
+  </si>
+  <si>
+    <t>Sauce Labs Fleece Jacket (49.99);SauceLabsOnesie(7.99)</t>
+  </si>
+  <si>
+    <t>Badge ẩn; nút của Fleece Jacket và Onesie đều là «Add to cart»</t>
+  </si>
+  <si>
+    <t>Bấm «Add to cart» tại thẻ Sauce Labs Fleece Jacket</t>
+  </si>
+  <si>
+    <t>Bấm «Add to cart» tại thẻ Sauce Labs Onesie</t>
+  </si>
+  <si>
+    <t>Bấm «Remove» ngay tại thẻ Sauce Labs Fleece Jacket trên inventory.html</t>
+  </si>
+  <si>
+    <t>Nút trả về «Add to cart»; badge giảm còn «1»</t>
+  </si>
+  <si>
+    <t>Bấm biểu tượng giỏ hàng để kiểm tra nội dung giỏ</t>
+  </si>
+  <si>
+    <t>cart.html chỉ còn 1 hàng: Sauce Labs Onesie $7.99; không có Fleece Jacket</t>
+  </si>
+  <si>
+    <t>Tiếp tục mua sắm từ trang giỏ hàng</t>
+  </si>
+  <si>
+    <t>FR-02 (FR-02.7) — Kiểm thử dựa trên ca sử dụng, luồng A4 «Tiếp tục mua sắm» («extend» Xem giỏ hàng)</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập thành công bằng tài khoản standard_user; giỏ đã có sẵn 1 sản phẩm — Sauce Labs Backpack $29.99 (thêm ở bước chuẩn bị)</t>
+  </si>
+  <si>
+    <t>Sauce Labs Backpack ($29.99)</t>
+  </si>
+  <si>
+    <t>Mở cart.html hiển thị đúng 1 hàng: Sauce Labs Backpack $29.99</t>
+  </si>
+  <si>
+    <t>Quay về inventory.html</t>
+  </si>
+  <si>
+    <t>Quan sát trạng thái nút và badge tại inventory.html</t>
+  </si>
+  <si>
+    <t>Nút Backpack vẫn là «Remove»; badge giữ «1» — trạng thái giỏ giữ nguyên như trước khi mở giỏ</t>
+  </si>
+  <si>
+    <t>Điền hợp lệ tất cả thông tin Checkout Step One</t>
+  </si>
+  <si>
+    <t>FR-03.1 — Bảng quyết định (DT - Quy tắc R1: Cả 3 trường hợp lệ)</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập bằng standard_user, có sản phẩm trong giỏ hàng và đang ở trang checkout-step-one.html</t>
+  </si>
+  <si>
+    <t>First Name: "Nguyen" | Last Name: "Van A" (hoặc "An") | Zip/Postal Code: "70000"</t>
+  </si>
+  <si>
+    <t>Nhập «Nguyen» vào trường First Name</t>
+  </si>
+  <si>
+    <t>Trường First Name hiển thị «Nguyen»</t>
+  </si>
+  <si>
+    <t>Nhập «Van A» vào trường Last Name</t>
+  </si>
+  <si>
+    <t>Trường Last Name hiển thị «Van A»</t>
+  </si>
+  <si>
+    <t>Nhập «70000» vào trường Zip/Postal Code</t>
+  </si>
+  <si>
+    <t>Trường Zip/Postal Code hiển thị «70000»</t>
+  </si>
+  <si>
+    <t>Bấm nút «Continue»</t>
+  </si>
+  <si>
+    <t>Không xuất hiện thông báo lỗi nào; hệ thống chuyển thành công sang trang xác nhận checkout-step-two.html</t>
+  </si>
+  <si>
+    <t>TC-CHK-DT-02</t>
+  </si>
+  <si>
+    <t>Bỏ trống First Name tại Checkout Step One</t>
+  </si>
+  <si>
+    <t>FR-03.2 — Bảng quyết định (DT - Quy tắc R2: Lỗi thiếu First Name)</t>
+  </si>
+  <si>
+    <t>First Name: "" (rỗng) | Last Name: "Van A" | Zip/Postal Code: "70000"</t>
+  </si>
+  <si>
+    <t>Để trống trường First Name (không nhập dữ liệu)</t>
+  </si>
+  <si>
+    <t>Trường First Name giữ trạng thái rỗng</t>
+  </si>
+  <si>
+    <t>Ở lại trang checkout-step-one.html; hiển thị thông báo lỗi: «Error: First Name is required»</t>
+  </si>
+  <si>
+    <t>TC-CHK-DT-03</t>
+  </si>
+  <si>
+    <t>Bỏ trống Last Name tại Checkout Step One</t>
+  </si>
+  <si>
+    <t>FR-03.2 — Bảng quyết định (DT - Quy tắc R3: Lỗi thiếu Last Name)</t>
+  </si>
+  <si>
+    <t>First Name: "Nguyen" | Last Name: "" (rỗng) | Zip/Postal Code: "70000"</t>
+  </si>
+  <si>
+    <t>Để trống trường Last Name (không nhập dữ liệu)</t>
+  </si>
+  <si>
+    <t>Trường Last Name giữ trạng thái rỗng</t>
+  </si>
+  <si>
+    <t>Ở lại trang checkout-step-one.html; hiển thị thông báo lỗi: «Error: Last Name is required»</t>
+  </si>
+  <si>
+    <t>TC-CHK-DT-04</t>
+  </si>
+  <si>
+    <t>Bỏ trống Postal Code tại Checkout Step One</t>
+  </si>
+  <si>
+    <t>FR-03.2 — Bảng quyết định (DT - Quy tắc R4: Lỗi thiếu Zip/Postal Code)</t>
+  </si>
+  <si>
+    <t>First Name: "Nguyen" | Last Name: "Van A" | Zip/Postal Code: "" (rỗng)</t>
+  </si>
+  <si>
+    <t>Để trống trường Zip/Postal Code (không nhập dữ liệu)</t>
+  </si>
+  <si>
+    <t>Trường Zip/Postal Code giữ trạng thái rỗng</t>
+  </si>
+  <si>
+    <t>Ở lại trang checkout-step-one.html; hiển thị thông báo lỗi: «Error: Postal Code is required»</t>
+  </si>
+  <si>
+    <t>Hủy thao tác tại màn hình nhập thông tin (Checkout Step One)</t>
+  </si>
+  <si>
+    <t>FR-03.3 — Kiểm thử dựa trên ca sử dụng, luồng rẽ nhánh UC-Alt (Cancel Step One)</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập, có sản phẩm trong giỏ hàng và đang ở màn hình nhập thông tin checkout-step-one.html</t>
+  </si>
+  <si>
+    <t>Sản phẩm có sẵn trong giỏ hàng; thao tác nhấn nút «Cancel»</t>
+  </si>
+  <si>
+    <t>Quan sát trạng thái tại trang checkout-step-one.html</t>
+  </si>
+  <si>
+    <t>Hiển thị các trường nhập thông tin giao hàng, nút «Cancel» và nút «Continue»</t>
+  </si>
+  <si>
+    <t>Bấm nút «Cancel»</t>
+  </si>
+  <si>
+    <t>Hệ thống hủy thao tác thanh toán và điều hướng quay về trang giỏ hàng cart.html</t>
+  </si>
+  <si>
+    <t>Kiểm tra danh sách sản phẩm trong giỏ hàng tại cart.html</t>
+  </si>
+  <si>
+    <t>Các sản phẩm đã thêm trong giỏ hàng được giữ nguyên, không bị mất</t>
+  </si>
+  <si>
+    <t>Kiểm tra hiển thị và công thức tính thuế 8% cùng Tổng tiền tại Step Two</t>
+  </si>
+  <si>
+    <t>FR-03.4 — Kiểm thử công thức tính toán (UC-Calculation)</t>
+  </si>
+  <si>
+    <t>Người dùng đã thêm sản phẩm Sauce Labs Backpack ($29.99) vào giỏ và hoàn tất Step One để vào trang checkout-step-two.html</t>
+  </si>
+  <si>
+    <t>Sản phẩm: Sauce Labs Backpack ($29.99) | Thuế suất: 8%</t>
+  </si>
+  <si>
+    <t>Quan sát thông tin đơn hàng tại trang checkout-step-two.html</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng sản phẩm Sauce Labs Backpack với đơn giá $29.99</t>
+  </si>
+  <si>
+    <t>Kiểm tra giá trị trường Item total</t>
+  </si>
+  <si>
+    <t>Hiển thị chính xác «Item total: $29.99»</t>
+  </si>
+  <si>
+    <t>Kiểm tra giá trị trường Tax (8%)</t>
+  </si>
+  <si>
+    <t>Hiển thị chính xác «Tax: $2.40» (tính từ 29.99 * 0.08 = 2.3992 làm tròn đến 2 chữ số thập phân)</t>
+  </si>
+  <si>
+    <t>Kiểm tra giá trị trường Total</t>
+  </si>
+  <si>
+    <t>Hiển thị chính xác «Total: $32.39» (= 29.99 + 2.40)</t>
+  </si>
+  <si>
+    <t>TC-CHK-UC-01</t>
+  </si>
+  <si>
+    <t>Hoàn tất đặt hàng thành công (Luồng chính Use Case Thanh toán)</t>
+  </si>
+  <si>
+    <t>FR-03.5 — Kiểm thử dựa trên ca sử dụng, luồng chính UC-Main</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập bằng standard_user và có sản phẩm trong giỏ hàng tại trang cart.html</t>
+  </si>
+  <si>
+    <t>First Name: "Nguyen" | Last Name: "Van A" | Zip/Postal Code: "70000"</t>
+  </si>
+  <si>
+    <t>Tại trang cart.html, bấm nút «Checkout»</t>
+  </si>
+  <si>
+    <t>Điều hướng sang trang nhập thông tin checkout-step-one.html</t>
+  </si>
+  <si>
+    <t>Nhập đầy đủ 3 trường hợp lệ («Nguyen», «Van A», «70000») và bấm nút «Continue»</t>
+  </si>
+  <si>
+    <t>Điều hướng sang trang xác nhận đơn hàng checkout-step-two.html</t>
+  </si>
+  <si>
+    <t>Kiểm tra thông tin tóm tắt đơn hàng và bấm nút «Finish»</t>
+  </si>
+  <si>
+    <t>Chuyển đến trang checkout-complete.html; hiển thị tiêu đề «Thank you for your order!», nút «Back Home» và badge giỏ hàng được làm rỗng</t>
+  </si>
+  <si>
+    <t>Sắp xếp sản phẩm theo tên từ A đến Z</t>
+  </si>
+  <si>
+    <t>FR-04.1 — Phân vùng tương đương (EP)</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập bằng tài khoản standard_user, trình duyệt đang ở URL inventory.html</t>
+  </si>
+  <si>
+    <t>Tùy chọn sắp xếp: Name (A to Z) (giá trị thuộc tính value="az")</t>
+  </si>
+  <si>
+    <t>Xác định thẻ dropdown menu sắp xếp có locator [data-test='product-sort-container'] trên trang inventory.html</t>
+  </si>
+  <si>
+    <t>Dropdown hiển thị rõ ràng trên góc phải danh sách sản phẩm</t>
+  </si>
+  <si>
+    <t>Chọn tùy chọn «Name (A to Z)» (giá trị value="az") từ dropdown menu</t>
+  </si>
+  <si>
+    <t>Giá trị hiển thị trên dropdown là «Name (A to Z)»</t>
+  </si>
+  <si>
+    <t>Đọc toàn bộ tên của 6 sản phẩm theo thứ tự hiển thị từ trên xuống dưới</t>
+  </si>
+  <si>
+    <t>Danh sách tên hiển thị đúng thứ tự bảng chữ cái Alphabet (A -&gt; Z): Sauce Labs Backpack -&gt; Sauce Labs Bike Light -&gt; Sauce Labs Bolt T-Shirt -&gt; Sauce Labs Fleece Jacket -&gt; Sauce Labs Onesie -&gt; Test.allTheThings() T-Shirt (Red)</t>
+  </si>
+  <si>
+    <t>Sắp xếp sản phẩm theo tên từ Z đến A</t>
+  </si>
+  <si>
+    <t>FR-04.2 — Phân vùng tương đương (EP)</t>
+  </si>
+  <si>
+    <t>Tùy chọn sắp xếp: Name (Z to A) (giá trị thuộc tính value="za")</t>
+  </si>
+  <si>
+    <t>Dropdown hiển thị rõ ràng, mặc định đang là «Name (A to Z)»</t>
+  </si>
+  <si>
+    <t>Chọn tùy chọn «Name (Z to A)» (giá trị value="za") từ dropdown menu</t>
+  </si>
+  <si>
+    <t>Giá trị hiển thị trên dropdown chuyển thành «Name (Z to A)»</t>
+  </si>
+  <si>
+    <t>Danh sách tên hiển thị đảo ngược đúng thứ tự (Z -&gt; A): Test.allTheThings() T-Shirt (Red) -&gt; Sauce Labs Onesie -&gt; Sauce Labs Fleece Jacket -&gt; Sauce Labs Bolt T-Shirt -&gt; Sauce Labs Bike Light -&gt; Sauce Labs Backpack</t>
+  </si>
+  <si>
+    <t>Sắp xếp sản phẩm theo giá từ thấp đến cao</t>
+  </si>
+  <si>
+    <t>FR-04.3 — Phân tích giá trị biên (BVA) &amp; Phân lớp tương đương (EP)</t>
+  </si>
+  <si>
+    <t>Đăng nhập tài khoản standard_user, trình duyệt đang ở URL inventory.html</t>
+  </si>
+  <si>
+    <t>Tùy chọn sắp xếp: Price (low to high) (giá trị thuộc tính value="lohi")</t>
+  </si>
+  <si>
+    <t>Dropdown hiển thị rõ ràng, giá trị hiện tại mặc định là Name (A to Z)</t>
+  </si>
+  <si>
+    <t>Chọn giá trị «Price (low to high)» (value="lohi") từ dropdown menu</t>
+  </si>
+  <si>
+    <t>Giá trị hiển thị trên dropdown chuyển thành «Price (low to high)»</t>
+  </si>
+  <si>
+    <t>Đọc toàn bộ đơn giá của 6 sản phẩm theo thứ tự hiển thị từ trên xuống dưới</t>
+  </si>
+  <si>
+    <t>Thứ tự giá trích xuất được tăng dần: $7.99 &lt;= $9.99 &lt;= $15.99 &lt;= $15.99 &lt;= $29.99 &lt;= $49.99; toàn bộ 6 sản phẩm vẫn hiển thị đầy đủ thông tin</t>
+  </si>
+  <si>
+    <t>Sắp xếp sản phẩm theo giá từ cao xuống thấp</t>
+  </si>
+  <si>
+    <t>FR-04.4 — Phân tích giá trị biên (BVA) &amp; Phân lớp tương đương (EP)</t>
+  </si>
+  <si>
+    <t>Tùy chọn sắp xếp: Price (high to low) (giá trị thuộc tính value="hilo")</t>
+  </si>
+  <si>
+    <t>Chọn giá trị «Price (high to low)» (value="hilo") từ dropdown menu</t>
+  </si>
+  <si>
+    <t>Giá trị hiển thị trên dropdown chuyển thành «Price (high to low)»</t>
+  </si>
+  <si>
+    <t>Thứ tự giá trích xuất được giảm dần: $49.99 &gt;= $29.99 &gt;= $15.99 &gt;= $15.99 &gt;= $9.99 &gt;= $7.99; toàn bộ 6 sản phẩm vẫn hiển thị đầy đủ thông tin</t>
+  </si>
+  <si>
+    <t>Execution ID</t>
+  </si>
+  <si>
+    <t>TestCase ID</t>
+  </si>
+  <si>
+    <t>Tested By</t>
+  </si>
+  <si>
+    <t>Execution Type</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Test Description</t>
-  </si>
-  <si>
-    <t>Input Data</t>
+    <t>EXEC-01</t>
+  </si>
+  <si>
+    <t>JUnit 5 Auto</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công, điều hướng chuẩn sang inventory.html</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>EXEC-02</t>
+  </si>
+  <si>
+    <t>Hiển thị chính xác thông báo lỗi tài khoản bị khóa</t>
+  </si>
+  <si>
+    <t>EXEC-03</t>
+  </si>
+  <si>
+    <t>Hiển thị chính xác thông báo Username is required</t>
+  </si>
+  <si>
+    <t>EXEC-04</t>
+  </si>
+  <si>
+    <t>Hiển thị chính xác thông báo Password is required</t>
+  </si>
+  <si>
+    <t>EXEC-05</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng lỗi sai thông tin đăng nhập</t>
+  </si>
+  <si>
+    <t>EXEC-06</t>
+  </si>
+  <si>
+    <t>Thời gian phản hồi tải trang là 5200 ms (vượt ngưỡng 3000 ms)</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>EXEC-07</t>
+  </si>
+  <si>
+    <t>Manual / Auto</t>
+  </si>
+  <si>
+    <t>Badge giỏ hàng ẩn hoàn toàn khi giỏ rỗng</t>
+  </si>
+  <si>
+    <t>EXEC-08</t>
+  </si>
+  <si>
+    <t>Badge tăng lên 1, nút đổi thành Remove</t>
+  </si>
+  <si>
+    <t>EXEC-09</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm thành công, cập nhật badge đúng</t>
+  </si>
+  <si>
+    <t>EXEC-10</t>
+  </si>
+  <si>
+    <t>Các thẻ sản phẩm đều hiển thị duy nhất 1 nút Add to cart</t>
+  </si>
+  <si>
+    <t>EXEC-11</t>
+  </si>
+  <si>
+    <t>Đã thêm cả 6 sản phẩm, badge hiển thị số 6 chính xác</t>
+  </si>
+  <si>
+    <t>EXEC-12</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng tên, mô tả và giá các món trong giỏ</t>
+  </si>
+  <si>
+    <t>EXEC-13</t>
+  </si>
+  <si>
+    <t>Sản phẩm bị xóa khỏi giỏ, badge giảm đúng 1</t>
+  </si>
+  <si>
+    <t>EXEC-14</t>
+  </si>
+  <si>
+    <t>Điều hướng về inventory.html giữ nguyên các món trong giỏ</t>
+  </si>
+  <si>
+    <t>EXEC-15</t>
+  </si>
+  <si>
+    <t>Điều hướng sang trang Step Two thành công</t>
+  </si>
+  <si>
+    <t>EXEC-16</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng thông báo lỗi Error: First Name is required</t>
+  </si>
+  <si>
+    <t>EXEC-17</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng thông báo lỗi Error: Last Name is required</t>
+  </si>
+  <si>
+    <t>EXEC-18</t>
+  </si>
+  <si>
+    <t>Hiển thị đúng thông báo lỗi Error: Postal Code is required</t>
+  </si>
+  <si>
+    <t>EXEC-19</t>
+  </si>
+  <si>
+    <t>Trở về cart.html và giữ nguyên giỏ hàng</t>
+  </si>
+  <si>
+    <t>EXEC-20</t>
+  </si>
+  <si>
+    <t>Thuế 8% tính $2.40, Tổng tiền $32.39 khớp công thức chuẩn</t>
+  </si>
+  <si>
+    <t>EXEC-21</t>
+  </si>
+  <si>
+    <t>Mở trang Complete, hiện thông báo cảm ơn, làm trống giỏ hàng</t>
+  </si>
+  <si>
+    <t>EXEC-22</t>
+  </si>
+  <si>
+    <t>Danh sách sản phẩm sắp xếp chuẩn theo thứ tự A-Z</t>
+  </si>
+  <si>
+    <t>EXEC-23</t>
+  </si>
+  <si>
+    <t>Danh sách sản phẩm sắp xếp chuẩn theo thứ tự Z-A</t>
+  </si>
+  <si>
+    <t>EXEC-24</t>
+  </si>
+  <si>
+    <t>Đơn giá hiển thị đúng thứ tự tăng dần từ $7.99 đến $49.99</t>
+  </si>
+  <si>
+    <t>EXEC-25</t>
+  </si>
+  <si>
+    <t>Đơn giá hiển thị đúng thứ tự giảm dần từ $49.99 đến $7.99</t>
+  </si>
+  <si>
+    <t>Bug ID</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Associated TC</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Steps to Reproduce</t>
   </si>
   <si>
     <t>Expected Result</t>
-  </si>
-  <si>
-    <t>EP</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công với tài khoản chuẩn</t>
-  </si>
-  <si>
-    <t>standard_user / secret_sauce</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công, mở trang inventory.html</t>
-  </si>
-  <si>
-    <t>Đăng nhập tài khoản bị khóa</t>
-  </si>
-  <si>
-    <t>locked_out_user / secret_sauce</t>
-  </si>
-  <si>
-    <t>Báo lỗi: Sorry, this user has been locked out</t>
-  </si>
-  <si>
-    <t>TC-LOGIN-DT-01</t>
-  </si>
-  <si>
-    <t>DT</t>
-  </si>
-  <si>
-    <t>Để trống Username khi đăng nhập</t>
-  </si>
-  <si>
-    <t>Username: "", Password: "secret_sauce"</t>
-  </si>
-  <si>
-    <t>Báo lỗi: Epic sadface: Username is required</t>
-  </si>
-  <si>
-    <t>TC-LOGIN-DT-02</t>
-  </si>
-  <si>
-    <t>Để trống Password khi đăng nhập</t>
-  </si>
-  <si>
-    <t>Username: "standard_user", Password: ""</t>
-  </si>
-  <si>
-    <t>Báo lỗi: Epic sadface: Password is required</t>
-  </si>
-  <si>
-    <t>Đăng nhập sai Mật khẩu</t>
-  </si>
-  <si>
-    <t>standard_user / wrong_password</t>
-  </si>
-  <si>
-    <t>Báo lỗi: Epic sadface: Username and password do not match...</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>Đo thời gian phản hồi trang sản phẩm</t>
-  </si>
-  <si>
-    <t>performance_glitch_user / secret_sauce</t>
-  </si>
-  <si>
-    <t>Thời gian phản hồi/tải trang &lt;= 3000 ms</t>
-  </si>
-  <si>
-    <t>TC-CART-B1</t>
-  </si>
-  <si>
-    <t>BVA</t>
-  </si>
-  <si>
-    <t>Kiểm tra giỏ hàng trống ban đầu (N=0)</t>
-  </si>
-  <si>
-    <t>Đã đăng nhập, giỏ rỗng</t>
-  </si>
-  <si>
-    <t>Badge giỏ hàng bị ẩn, không hiển thị số 0</t>
-  </si>
-  <si>
-    <t>TC-CART-B2</t>
-  </si>
-  <si>
-    <t>Kiểm tra badge khi thêm 1 sản phẩm (N=1)</t>
-  </si>
-  <si>
-    <t>Click Add to cart 1 sản phẩm</t>
-  </si>
-  <si>
-    <t>Badge hiển thị "1", nút đổi thành Remove</t>
-  </si>
-  <si>
-    <t>TC-CART-B3</t>
-  </si>
-  <si>
-    <t>Thêm sản phẩm từ trang inventory</t>
-  </si>
-  <si>
-    <t>Click Add to cart sản phẩm Backpack</t>
-  </si>
-  <si>
-    <t>Badge tăng thêm 1, nút chuyển thành Remove</t>
-  </si>
-  <si>
-    <t>TC-CART-B4</t>
-  </si>
-  <si>
-    <t>Kiểm tra nút bấm trên thẻ sản phẩm</t>
-  </si>
-  <si>
-    <t>Trang inventory.html</t>
-  </si>
-  <si>
-    <t>Mỗi sản phẩm có đúng 1 nút Add to cart</t>
-  </si>
-  <si>
-    <t>TC-CART-B5</t>
-  </si>
-  <si>
-    <t>Thêm tối đa 6 sản phẩm vào giỏ (N=6)</t>
-  </si>
-  <si>
-    <t>Click Add to cart cả 6 sản phẩm</t>
-  </si>
-  <si>
-    <t>Badge hiển thị "6", tất cả nút chuyển thành Remove</t>
-  </si>
-  <si>
-    <t>TC-CART-UC1</t>
-  </si>
-  <si>
-    <t>Use Case</t>
-  </si>
-  <si>
-    <t>Kiểm tra hiển thị danh sách trong cart.html</t>
-  </si>
-  <si>
-    <t>Thêm 2 sản phẩm vào giỏ -&gt; Mở cart.html</t>
-  </si>
-  <si>
-    <t>Hiển thị đúng tên, mô tả và đơn giá của 2 sản phẩm</t>
-  </si>
-  <si>
-    <t>TC-CART-UC3</t>
-  </si>
-  <si>
-    <t>Xóa sản phẩm tại trang cart.html</t>
-  </si>
-  <si>
-    <t>Mở cart.html -&gt; Click Remove ở sản phẩm 1</t>
-  </si>
-  <si>
-    <t>Sản phẩm bị loại khỏi danh sách, Badge giảm 1</t>
-  </si>
-  <si>
-    <t>Chức năng Continue Shopping</t>
-  </si>
-  <si>
-    <t>Mở cart.html -&gt; Click Continue Shopping</t>
-  </si>
-  <si>
-    <t>Quay lại inventory.html, trạng thái giỏ được giữ nguyên</t>
-  </si>
-  <si>
-    <t>Điền hợp lệ tất cả thông tin Checkout Step One</t>
-  </si>
-  <si>
-    <t>First: "Nguyen", Last: "An", Zip: "70000"</t>
-  </si>
-  <si>
-    <t>Chuyển thành công sang trang checkout-step-two.html</t>
-  </si>
-  <si>
-    <t>TC-CHK-DT-02</t>
-  </si>
-  <si>
-    <t>Bỏ trống First Name tại Step One</t>
-  </si>
-  <si>
-    <t>First: "", Last: "An", Zip: "70000"</t>
-  </si>
-  <si>
-    <t>Hiển thị lỗi: Error: First Name is required</t>
-  </si>
-  <si>
-    <t>TC-CHK-DT-03</t>
-  </si>
-  <si>
-    <t>Bỏ trống Last Name tại Step One</t>
-  </si>
-  <si>
-    <t>First: "Nguyen", Last: "", Zip: "70000"</t>
-  </si>
-  <si>
-    <t>Hiển thị lỗi: Error: Last Name is required</t>
-  </si>
-  <si>
-    <t>TC-CHK-DT-04</t>
-  </si>
-  <si>
-    <t>Bỏ trống Postal Code tại Step One</t>
-  </si>
-  <si>
-    <t>First: "Nguyen", Last: "An", Zip: ""</t>
-  </si>
-  <si>
-    <t>Hiển thị lỗi: Error: Postal Code is required</t>
-  </si>
-  <si>
-    <t>Hủy thao tác tại Step One</t>
-  </si>
-  <si>
-    <t>Click Cancel tại Step One</t>
-  </si>
-  <si>
-    <t>Quay lại cart.html, giữ nguyên danh sách sản phẩm</t>
-  </si>
-  <si>
-    <t>Calculation</t>
-  </si>
-  <si>
-    <t>Kiểm tra công thức tính thuế 8% và Tổng tiền</t>
-  </si>
-  <si>
-    <t>Sản phẩm $29.99 trong giỏ</t>
-  </si>
-  <si>
-    <t>Item total: $29.99, Tax: $2.40, Total: $32.39</t>
-  </si>
-  <si>
-    <t>TC-CHK-UC-01</t>
-  </si>
-  <si>
-    <t>Hoàn tất đặt hàng thành công</t>
-  </si>
-  <si>
-    <t>Click Finish tại Step Two</t>
-  </si>
-  <si>
-    <t>Mở checkout-complete.html, hiện Thank you..., giỏ làm rỗng</t>
-  </si>
-  <si>
-    <t>Sắp xếp sản phẩm theo tên A-Z</t>
-  </si>
-  <si>
-    <t>Select option "Name (A to Z)"</t>
-  </si>
-  <si>
-    <t>Danh sách sản phẩm sắp xếp chuẩn theo thứ tự A-Z</t>
-  </si>
-  <si>
-    <t>Sắp xếp sản phẩm theo tên Z-A</t>
-  </si>
-  <si>
-    <t>Select option "Name (Z to A)"</t>
-  </si>
-  <si>
-    <t>Danh sách sản phẩm sắp xếp chuẩn theo thứ tự Z-A</t>
-  </si>
-  <si>
-    <t>Sắp xếp sản phẩm theo giá thấp đến cao</t>
-  </si>
-  <si>
-    <t>Select option "Price (low to high)"</t>
-  </si>
-  <si>
-    <t>Danh sách sản phẩm sắp xếp giá tăng dần ($7.99 -&gt; $49.99)</t>
-  </si>
-  <si>
-    <t>Sắp xếp sản phẩm theo giá cao xuống thấp</t>
-  </si>
-  <si>
-    <t>Select option "Price (high to low)"</t>
-  </si>
-  <si>
-    <t>Danh sách sản phẩm sắp xếp giá giảm dần ($49.99 -&gt; $7.99)</t>
-  </si>
-  <si>
-    <t>Execution ID</t>
-  </si>
-  <si>
-    <t>TestCase ID</t>
-  </si>
-  <si>
-    <t>Tested By</t>
-  </si>
-  <si>
-    <t>Execution Type</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
-    <t>EXEC-01</t>
-  </si>
-  <si>
-    <t>JUnit 5 Auto</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công, điều hướng chuẩn sang inventory.html</t>
-  </si>
-  <si>
-    <t>EXEC-02</t>
-  </si>
-  <si>
-    <t>Hiển thị chính xác thông báo lỗi tài khoản bị khóa</t>
-  </si>
-  <si>
-    <t>EXEC-03</t>
-  </si>
-  <si>
-    <t>Hiển thị chính xác thông báo Username is required</t>
-  </si>
-  <si>
-    <t>EXEC-04</t>
-  </si>
-  <si>
-    <t>Hiển thị chính xác thông báo Password is required</t>
-  </si>
-  <si>
-    <t>EXEC-05</t>
-  </si>
-  <si>
-    <t>Hiển thị đúng lỗi sai thông tin đăng nhập</t>
-  </si>
-  <si>
-    <t>EXEC-06</t>
-  </si>
-  <si>
-    <t>Thời gian phản hồi tải trang là 5200 ms (vượt ngưỡng 3000 ms)</t>
-  </si>
-  <si>
-    <t>EXEC-07</t>
-  </si>
-  <si>
-    <t>Manual / Auto</t>
-  </si>
-  <si>
-    <t>Badge giỏ hàng ẩn hoàn toàn khi giỏ rỗng</t>
-  </si>
-  <si>
-    <t>EXEC-08</t>
-  </si>
-  <si>
-    <t>Badge tăng lên 1, nút đổi thành Remove</t>
-  </si>
-  <si>
-    <t>EXEC-09</t>
-  </si>
-  <si>
-    <t>Thêm sản phẩm thành công, cập nhật badge đúng</t>
-  </si>
-  <si>
-    <t>EXEC-10</t>
-  </si>
-  <si>
-    <t>Các thẻ sản phẩm đều hiển thị duy nhất 1 nút Add to cart</t>
-  </si>
-  <si>
-    <t>EXEC-11</t>
-  </si>
-  <si>
-    <t>Đã thêm cả 6 sản phẩm, badge hiển thị số 6 chính xác</t>
-  </si>
-  <si>
-    <t>EXEC-12</t>
-  </si>
-  <si>
-    <t>Hiển thị đúng tên, mô tả và giá các món trong giỏ</t>
-  </si>
-  <si>
-    <t>EXEC-13</t>
-  </si>
-  <si>
-    <t>Sản phẩm bị xóa khỏi giỏ, badge giảm đúng 1</t>
-  </si>
-  <si>
-    <t>EXEC-14</t>
-  </si>
-  <si>
-    <t>Điều hướng về inventory.html giữ nguyên các món trong giỏ</t>
-  </si>
-  <si>
-    <t>EXEC-15</t>
-  </si>
-  <si>
-    <t>Điều hướng sang trang Step Two thành công</t>
-  </si>
-  <si>
-    <t>EXEC-16</t>
-  </si>
-  <si>
-    <t>Hiển thị đúng thông báo lỗi Error: First Name is required</t>
-  </si>
-  <si>
-    <t>EXEC-17</t>
-  </si>
-  <si>
-    <t>Hiển thị đúng thông báo lỗi Error: Last Name is required</t>
-  </si>
-  <si>
-    <t>EXEC-18</t>
-  </si>
-  <si>
-    <t>Hiển thị đúng thông báo lỗi Error: Postal Code is required</t>
-  </si>
-  <si>
-    <t>EXEC-19</t>
-  </si>
-  <si>
-    <t>Trở về cart.html và giữ nguyên giỏ hàng</t>
-  </si>
-  <si>
-    <t>EXEC-20</t>
-  </si>
-  <si>
-    <t>Thuế 8% tính $2.40, Tổng tiền $32.39 khớp công thức chuẩn</t>
-  </si>
-  <si>
-    <t>EXEC-21</t>
-  </si>
-  <si>
-    <t>Mở trang Complete, hiện thông báo cảm ơn, làm trống giỏ hàng</t>
-  </si>
-  <si>
-    <t>EXEC-22</t>
-  </si>
-  <si>
-    <t>EXEC-23</t>
-  </si>
-  <si>
-    <t>EXEC-24</t>
-  </si>
-  <si>
-    <t>Đơn giá hiển thị đúng thứ tự tăng dần từ $7.99 đến $49.99</t>
-  </si>
-  <si>
-    <t>EXEC-25</t>
-  </si>
-  <si>
-    <t>Đơn giá hiển thị đúng thứ tự giảm dần từ $49.99 đến $7.99</t>
-  </si>
-  <si>
-    <t>Bug ID</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Associated TC</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Steps to Reproduce</t>
   </si>
   <si>
     <t>BUG-01</t>
@@ -802,6 +1234,9 @@
 2. Nhập username: performance_glitch_user
 3. Nhập password: secret_sauce
 4. Đo thời gian tải trang inventory.html</t>
+  </si>
+  <si>
+    <t>Thời gian phản hồi/tải trang &lt;= 3000 ms</t>
   </si>
   <si>
     <t>Thời gian phản hồi thực tế kéo dài tới ~5200 ms</t>
@@ -873,7 +1308,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -891,6 +1326,39 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1040,7 +1508,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1063,6 +1531,24 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.25"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -1252,7 +1738,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="60">
     <border>
       <left/>
       <right/>
@@ -1302,6 +1788,620 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="2"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1423,137 +2523,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="52" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="55" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="56" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="55" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="57" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="58" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="59" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1584,11 +2684,257 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1609,7 +2955,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1648,7 +2994,31 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="24">
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <alignment wrapText="1"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1842,25 +3212,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="13"/>
+      <tableStyleElement type="headerRow" dxfId="12"/>
+      <tableStyleElement type="totalRow" dxfId="11"/>
+      <tableStyleElement type="firstColumn" dxfId="10"/>
+      <tableStyleElement type="lastColumn" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="23"/>
+      <tableStyleElement type="totalRow" dxfId="22"/>
+      <tableStyleElement type="firstRowStripe" dxfId="21"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="20"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="19"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="18"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="17"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="16"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="15"/>
+      <tableStyleElement type="pageFieldValues" dxfId="14"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1869,6 +3239,21 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G10" headerRowCount="0" totalsRowShown="0">
+  <tableColumns count="7">
+    <tableColumn id="1" name="Column1" dataDxfId="0"/>
+    <tableColumn id="2" name="Column2" dataDxfId="1"/>
+    <tableColumn id="3" name="Column3" dataDxfId="2"/>
+    <tableColumn id="4" name="Column4" dataDxfId="3"/>
+    <tableColumn id="5" name="Column5" dataDxfId="4"/>
+    <tableColumn id="6" name="Column6" dataDxfId="5"/>
+    <tableColumn id="7" name="Column7" dataDxfId="6"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2149,359 +3534,359 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="93" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="94" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="94" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="94" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="94" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="94" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="95" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="95" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="95" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="95" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="95" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="95" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="95" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="95" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="95" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="95" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="95" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="95" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="95" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="95" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="95" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="95" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="95" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="95" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="95" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="95" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="95" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="95" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="95" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="95" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="95" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2541,359 +3926,359 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="93" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="93" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="94" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="94" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="94" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="94" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="94" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="95" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="95" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="95" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="95" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="95" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="95" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="95" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="95" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="95" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="95" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="95" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="95" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="95" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="95" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="95" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="95" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="95" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="95" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="95" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="95" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="95" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="95" t="s">
         <v>81</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="95" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="95" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="95" t="s">
         <v>81</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="95" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="95" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="95" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="95" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="95" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="95" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="95" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="95" t="s">
         <v>87</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="95" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="95" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="95" t="s">
         <v>88</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="95" t="s">
         <v>87</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="95" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="95" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="95" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="95" t="s">
         <v>87</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="95" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="95" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="95" t="s">
         <v>78</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="95" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="95" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="95" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2906,617 +4291,2506 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A1:I285"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="3" max="3" width="15.1111111111111" customWidth="1"/>
-    <col min="5" max="5" width="43.1111111111111" customWidth="1"/>
-    <col min="6" max="6" width="40.4444444444444" customWidth="1"/>
-    <col min="7" max="7" width="57.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="16.4444444444444" style="10" customWidth="1"/>
+    <col min="2" max="2" width="57" style="10" customWidth="1"/>
+    <col min="3" max="3" width="41.5555555555556" style="10" customWidth="1"/>
+    <col min="4" max="6" width="8.88888888888889" style="10"/>
+    <col min="7" max="7" width="8.88888888888889" style="11"/>
+    <col min="8" max="16384" width="8.88888888888889" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:7">
-      <c r="A1" s="1" t="s">
+    <row r="1" customHeight="1" spans="1:7">
+      <c r="A1" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:7">
+      <c r="A2" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C2" s="13"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:7">
+      <c r="A3" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B3" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="C3" s="13"/>
+      <c r="G3" s="14"/>
+    </row>
+    <row r="4" ht="28.8" customHeight="1" spans="1:7">
+      <c r="A4" s="16" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="B4" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:7">
+      <c r="A5" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="18"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" ht="28.8" spans="1:7">
+      <c r="A7" s="22">
+        <v>1</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="24">
+        <v>2</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="24">
+        <v>3</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" ht="28.8" spans="1:7">
+      <c r="A10" s="24">
+        <v>4</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" ht="16" customHeight="1" spans="1:7">
+      <c r="A11" s="25"/>
+      <c r="B11" s="26"/>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" customHeight="1"/>
+    <row r="13" customHeight="1" spans="1:4">
+      <c r="A13" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="29"/>
+      <c r="D13" s="30"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:4">
+      <c r="A14" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="32"/>
+      <c r="D14" s="30"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:4">
+      <c r="A15" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="32"/>
+      <c r="D15" s="30"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:9">
+      <c r="A16" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="35"/>
+      <c r="D16" s="36"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="55"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="38"/>
+      <c r="D17" s="30"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="30"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="10">
+        <v>1</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="30"/>
+      <c r="E19" s="37"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="44">
+        <v>2</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="30"/>
+      <c r="E20" s="37"/>
+    </row>
+    <row r="21" ht="28.8" spans="1:4">
+      <c r="A21" s="10">
+        <v>3</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" s="30"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="34"/>
+      <c r="C22" s="34"/>
+    </row>
+    <row r="23" customHeight="1"/>
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" s="35"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="35"/>
+    </row>
+    <row r="26" ht="28.8" customHeight="1" spans="1:3">
+      <c r="A26" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="35"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:3">
+      <c r="A27" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="C27" s="35"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" s="51"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" s="55"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="56">
+        <v>1</v>
+      </c>
+      <c r="B30" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="56" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="35">
+        <v>2</v>
+      </c>
+      <c r="B31" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" ht="28.8" spans="1:3">
+      <c r="A32" s="35">
+        <v>3</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1"/>
+    <row r="35" customHeight="1" spans="1:3">
+      <c r="A35" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" s="35"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:3">
+      <c r="A36" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36" s="35"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:3">
+      <c r="A37" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" s="35"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:3">
+      <c r="A38" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" s="35"/>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" s="51"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="59" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" s="60" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" s="30"/>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="56">
+        <v>1</v>
+      </c>
+      <c r="B41" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41" s="56" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="35">
+        <v>2</v>
+      </c>
+      <c r="B42" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" s="35" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="43" ht="28.8" spans="1:3">
+      <c r="A43" s="35">
+        <v>3</v>
+      </c>
+      <c r="B43" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C43" s="35" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="58" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" s="35"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:3">
+      <c r="A47" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="C47" s="35"/>
+    </row>
+    <row r="48" ht="28.8" customHeight="1" spans="1:3">
+      <c r="A48" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="C48" s="35"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:3">
+      <c r="A49" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="C49" s="35"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:3">
+      <c r="A50" s="58" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="C50" s="51"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:3">
+      <c r="A51" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" s="59" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" s="61" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="56">
+        <v>1</v>
+      </c>
+      <c r="B52" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="C52" s="56" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="35">
+        <v>2</v>
+      </c>
+      <c r="B53" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="C53" s="35" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" ht="43.2" spans="1:3">
+      <c r="A54" s="35">
+        <v>3</v>
+      </c>
+      <c r="B54" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" s="35" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B57" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" s="35"/>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B58" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="C58" s="35"/>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="B59" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="C59" s="35"/>
+    </row>
+    <row r="60" ht="28.8" spans="1:3">
+      <c r="A60" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B60" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="C60" s="35"/>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="B61" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="C61" s="51"/>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B62" s="59" t="s">
+        <v>101</v>
+      </c>
+      <c r="C62" s="61" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="63" ht="28.8" spans="1:3">
+      <c r="A63" s="56">
+        <v>1</v>
+      </c>
+      <c r="B63" s="56" t="s">
+        <v>141</v>
+      </c>
+      <c r="C63" s="56" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="35">
+        <v>2</v>
+      </c>
+      <c r="B64" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="C64" s="35" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="65" ht="43.2" spans="1:3">
+      <c r="A65" s="35">
+        <v>3</v>
+      </c>
+      <c r="B65" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="C65" s="35" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="62"/>
+      <c r="B67" s="63"/>
+      <c r="C67" s="63"/>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="B68" s="65" t="s">
+        <v>145</v>
+      </c>
+      <c r="C68" s="65"/>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="B69" s="67" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="65"/>
+    </row>
+    <row r="70" ht="27.6" spans="1:3">
+      <c r="A70" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="B70" s="68" t="s">
+        <v>147</v>
+      </c>
+      <c r="C70" s="65"/>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="B71" s="69" t="s">
+        <v>148</v>
+      </c>
+      <c r="C71" s="65"/>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="66" t="s">
+        <v>98</v>
+      </c>
+      <c r="B72" s="70" t="s">
+        <v>149</v>
+      </c>
+      <c r="C72" s="71"/>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="72" t="s">
+        <v>100</v>
+      </c>
+      <c r="B73" s="73" t="s">
+        <v>101</v>
+      </c>
+      <c r="C73" s="74" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="74" ht="27.6" spans="1:3">
+      <c r="A74" s="75">
+        <v>1</v>
+      </c>
+      <c r="B74" s="76" t="s">
+        <v>150</v>
+      </c>
+      <c r="C74" s="76" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="75" ht="27.6" spans="1:3">
+      <c r="A75" s="77">
+        <v>2</v>
+      </c>
+      <c r="B75" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="C75" s="65" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76"/>
+      <c r="B76"/>
+      <c r="C76"/>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77"/>
+      <c r="B77"/>
+      <c r="C77"/>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="78" t="s">
+        <v>91</v>
+      </c>
+      <c r="B78" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="C78" s="65"/>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="B79" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="C79" s="65"/>
+    </row>
+    <row r="80" ht="27.6" spans="1:3">
+      <c r="A80" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="B80" s="69" t="s">
+        <v>156</v>
+      </c>
+      <c r="C80" s="65"/>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="B81" s="69" t="s">
+        <v>157</v>
+      </c>
+      <c r="C81" s="65"/>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="79" t="s">
+        <v>98</v>
+      </c>
+      <c r="B82" s="70" t="s">
+        <v>158</v>
+      </c>
+      <c r="C82" s="71"/>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="B83" s="81" t="s">
+        <v>101</v>
+      </c>
+      <c r="C83" s="82" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="84" ht="27.6" spans="1:3">
+      <c r="A84" s="75">
+        <v>1</v>
+      </c>
+      <c r="B84" s="76" t="s">
+        <v>159</v>
+      </c>
+      <c r="C84" s="76" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="77">
+        <v>2</v>
+      </c>
+      <c r="B85" s="65" t="s">
+        <v>161</v>
+      </c>
+      <c r="C85" s="65" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="86" ht="27.6" spans="1:3">
+      <c r="A86" s="77">
+        <v>3</v>
+      </c>
+      <c r="B86" s="65" t="s">
+        <v>163</v>
+      </c>
+      <c r="C86" s="65" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87"/>
+      <c r="B87"/>
+      <c r="C87"/>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88"/>
+      <c r="B88"/>
+      <c r="C88"/>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="78" t="s">
+        <v>91</v>
+      </c>
+      <c r="B89" s="65" t="s">
+        <v>165</v>
+      </c>
+      <c r="C89" s="65"/>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="B90" s="69" t="s">
+        <v>166</v>
+      </c>
+      <c r="C90" s="65"/>
+    </row>
+    <row r="91" ht="27.6" spans="1:3">
+      <c r="A91" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="B91" s="69" t="s">
+        <v>167</v>
+      </c>
+      <c r="C91" s="65"/>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" s="69" t="s">
+        <v>168</v>
+      </c>
+      <c r="C92" s="65"/>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="79" t="s">
+        <v>98</v>
+      </c>
+      <c r="B93" s="70" t="s">
+        <v>169</v>
+      </c>
+      <c r="C93" s="71"/>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" s="81" t="s">
+        <v>101</v>
+      </c>
+      <c r="C94" s="82" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="75">
+        <v>1</v>
+      </c>
+      <c r="B95" s="76" t="s">
+        <v>170</v>
+      </c>
+      <c r="C95" s="76" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="77">
+        <v>2</v>
+      </c>
+      <c r="B96" s="65" t="s">
+        <v>172</v>
+      </c>
+      <c r="C96" s="65" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="97" ht="27.6" spans="1:3">
+      <c r="A97" s="77">
+        <v>3</v>
+      </c>
+      <c r="B97" s="65" t="s">
+        <v>174</v>
+      </c>
+      <c r="C97" s="65" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98"/>
+      <c r="B98"/>
+      <c r="C98"/>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99"/>
+      <c r="B99"/>
+      <c r="C99"/>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="78" t="s">
+        <v>91</v>
+      </c>
+      <c r="B100" s="65" t="s">
+        <v>176</v>
+      </c>
+      <c r="C100" s="65"/>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="B101" s="69" t="s">
+        <v>177</v>
+      </c>
+      <c r="C101" s="65"/>
+    </row>
+    <row r="102" ht="27.6" spans="1:3">
+      <c r="A102" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="B102" s="69" t="s">
+        <v>178</v>
+      </c>
+      <c r="C102" s="65"/>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="B103" s="69" t="s">
+        <v>168</v>
+      </c>
+      <c r="C103" s="65"/>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="79" t="s">
+        <v>98</v>
+      </c>
+      <c r="B104" s="70" t="s">
+        <v>179</v>
+      </c>
+      <c r="C104" s="71"/>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="B105" s="81" t="s">
+        <v>101</v>
+      </c>
+      <c r="C105" s="82" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="75">
+        <v>1</v>
+      </c>
+      <c r="B106" s="76" t="s">
+        <v>180</v>
+      </c>
+      <c r="C106" s="76" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="107" ht="27.6" spans="1:3">
+      <c r="A107" s="77">
+        <v>2</v>
+      </c>
+      <c r="B107" s="65" t="s">
+        <v>182</v>
+      </c>
+      <c r="C107" s="65" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="77">
+        <v>3</v>
+      </c>
+      <c r="B108" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="C108" s="65" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="109" ht="27.6" spans="1:3">
+      <c r="A109" s="77">
+        <v>4</v>
+      </c>
+      <c r="B109" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="C109" s="65" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="78" t="s">
+        <v>91</v>
+      </c>
+      <c r="B112" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="C112" s="65"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="B113" s="69" t="s">
+        <v>189</v>
+      </c>
+      <c r="C113" s="65"/>
+    </row>
+    <row r="114" ht="27.6" spans="1:3">
+      <c r="A114" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="B114" s="69" t="s">
+        <v>190</v>
+      </c>
+      <c r="C114" s="65"/>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="B115" s="69" t="s">
+        <v>168</v>
+      </c>
+      <c r="C115" s="65"/>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="79" t="s">
+        <v>98</v>
+      </c>
+      <c r="B116" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="C116" s="71"/>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="B117" s="81" t="s">
+        <v>101</v>
+      </c>
+      <c r="C117" s="82" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="75">
+        <v>1</v>
+      </c>
+      <c r="B118" s="76" t="s">
+        <v>180</v>
+      </c>
+      <c r="C118" s="76" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="119" ht="27.6" spans="1:3">
+      <c r="A119" s="77">
+        <v>2</v>
+      </c>
+      <c r="B119" s="65" t="s">
+        <v>192</v>
+      </c>
+      <c r="C119" s="65" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="120" ht="27.6" spans="1:3">
+      <c r="A120" s="77">
+        <v>3</v>
+      </c>
+      <c r="B120" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="C120" s="65" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="121" ht="27.6" spans="1:3">
+      <c r="A121" s="77">
+        <v>4</v>
+      </c>
+      <c r="B121" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="C121" s="65" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="78" t="s">
+        <v>91</v>
+      </c>
+      <c r="B124" s="65" t="s">
+        <v>196</v>
+      </c>
+      <c r="C124" s="65"/>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="B125" s="69" t="s">
+        <v>197</v>
+      </c>
+      <c r="C125" s="65"/>
+    </row>
+    <row r="126" ht="27.6" spans="1:3">
+      <c r="A126" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="B126" s="69" t="s">
+        <v>198</v>
+      </c>
+      <c r="C126" s="65"/>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="B127" s="69" t="s">
+        <v>199</v>
+      </c>
+      <c r="C127" s="65"/>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="79" t="s">
+        <v>98</v>
+      </c>
+      <c r="B128" s="70" t="s">
+        <v>200</v>
+      </c>
+      <c r="C128" s="71"/>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="B129" s="81" t="s">
+        <v>101</v>
+      </c>
+      <c r="C129" s="82" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="130" ht="27.6" spans="1:3">
+      <c r="A130" s="75">
+        <v>1</v>
+      </c>
+      <c r="B130" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="C130" s="76" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="77">
+        <v>2</v>
+      </c>
+      <c r="B131" s="65" t="s">
+        <v>203</v>
+      </c>
+      <c r="C131" s="65" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" s="77">
+        <v>3</v>
+      </c>
+      <c r="B132" s="65" t="s">
+        <v>205</v>
+      </c>
+      <c r="C132" s="65" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="133" ht="27.6" spans="1:3">
+      <c r="A133" s="77">
+        <v>4</v>
+      </c>
+      <c r="B133" s="65" t="s">
+        <v>207</v>
+      </c>
+      <c r="C133" s="65" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="134" ht="27.6" spans="1:3">
+      <c r="A134" s="77">
         <v>5</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="10" t="s">
+      <c r="B134" s="65" t="s">
+        <v>209</v>
+      </c>
+      <c r="C134" s="65" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="135" ht="27.6" spans="1:3">
+      <c r="A135" s="77">
+        <v>6</v>
+      </c>
+      <c r="B135" s="65" t="s">
+        <v>211</v>
+      </c>
+      <c r="C135" s="65" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" s="78" t="s">
+        <v>91</v>
+      </c>
+      <c r="B138" s="65" t="s">
+        <v>213</v>
+      </c>
+      <c r="C138" s="65"/>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" s="83" t="s">
+        <v>92</v>
+      </c>
+      <c r="B139" s="84" t="s">
+        <v>214</v>
+      </c>
+      <c r="C139" s="65"/>
+    </row>
+    <row r="140" ht="27.6" spans="1:3">
+      <c r="A140" s="83" t="s">
+        <v>94</v>
+      </c>
+      <c r="B140" s="84" t="s">
+        <v>215</v>
+      </c>
+      <c r="C140" s="65"/>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" s="83" t="s">
+        <v>96</v>
+      </c>
+      <c r="B141" s="84" t="s">
+        <v>199</v>
+      </c>
+      <c r="C141" s="65"/>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" s="79" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="F2" s="11" t="s">
+      <c r="B142" s="70" t="s">
+        <v>216</v>
+      </c>
+      <c r="C142" s="71"/>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="B143" s="81" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" s="12" t="s">
+      <c r="C143" s="82" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="144" ht="27.6" spans="1:3">
+      <c r="A144" s="75">
+        <v>1</v>
+      </c>
+      <c r="B144" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="C144" s="76" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" s="77">
+        <v>2</v>
+      </c>
+      <c r="B145" s="65" t="s">
+        <v>218</v>
+      </c>
+      <c r="C145" s="65" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="77">
+        <v>3</v>
+      </c>
+      <c r="B146" s="65" t="s">
+        <v>219</v>
+      </c>
+      <c r="C146" s="65" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="147" ht="27.6" spans="1:3">
+      <c r="A147" s="77">
+        <v>4</v>
+      </c>
+      <c r="B147" s="65" t="s">
+        <v>220</v>
+      </c>
+      <c r="C147" s="65" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="148" ht="27.6" spans="1:3">
+      <c r="A148" s="77">
+        <v>5</v>
+      </c>
+      <c r="B148" s="65" t="s">
+        <v>222</v>
+      </c>
+      <c r="C148" s="65" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" s="78" t="s">
+        <v>91</v>
+      </c>
+      <c r="B151" s="65" t="s">
+        <v>79</v>
+      </c>
+      <c r="C151" s="65"/>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="B152" s="69" t="s">
+        <v>224</v>
+      </c>
+      <c r="C152" s="65"/>
+      <c r="E152" s="35"/>
+    </row>
+    <row r="153" ht="27.6" spans="1:3">
+      <c r="A153" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="B153" s="69" t="s">
+        <v>225</v>
+      </c>
+      <c r="C153" s="85"/>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" s="83" t="s">
+        <v>96</v>
+      </c>
+      <c r="B154" s="84" t="s">
+        <v>226</v>
+      </c>
+      <c r="C154" s="65"/>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" s="83" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="B155" s="86" t="s">
+        <v>227</v>
+      </c>
+      <c r="C155" s="71"/>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="B156" s="81" t="s">
+        <v>101</v>
+      </c>
+      <c r="C156" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D4" s="12" t="s">
+    </row>
+    <row r="157" ht="27.6" spans="1:3">
+      <c r="A157" s="75">
+        <v>1</v>
+      </c>
+      <c r="B157" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="C157" s="76" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" s="77">
+        <v>2</v>
+      </c>
+      <c r="B158" s="65" t="s">
+        <v>211</v>
+      </c>
+      <c r="C158" s="65" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="159" ht="27.6" spans="1:3">
+      <c r="A159" s="77">
+        <v>3</v>
+      </c>
+      <c r="B159" s="65" t="s">
+        <v>230</v>
+      </c>
+      <c r="C159" s="65" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B162" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C162" s="35"/>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B163" s="48" t="s">
+        <v>232</v>
+      </c>
+      <c r="C163" s="35"/>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="B164" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="C164" s="35"/>
+    </row>
+    <row r="165" ht="28.8" spans="1:3">
+      <c r="A165" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B165" s="48" t="s">
+        <v>234</v>
+      </c>
+      <c r="C165" s="35"/>
+    </row>
+    <row r="166" ht="28.8" spans="1:3">
+      <c r="A166" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="E4" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D5" s="12" t="s">
+      <c r="B166" s="51" t="s">
+        <v>235</v>
+      </c>
+      <c r="C166" s="51"/>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B167" s="87" t="s">
+        <v>101</v>
+      </c>
+      <c r="C167" s="87" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" s="56">
+        <v>1</v>
+      </c>
+      <c r="B168" s="56" t="s">
+        <v>236</v>
+      </c>
+      <c r="C168" s="56" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" s="35">
+        <v>2</v>
+      </c>
+      <c r="B169" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="C169" s="35" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170" s="35">
+        <v>3</v>
+      </c>
+      <c r="B170" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="C170" s="35" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="171" ht="43.2" spans="1:3">
+      <c r="A171" s="35">
+        <v>4</v>
+      </c>
+      <c r="B171" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="C171" s="35" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B174" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="C174" s="35"/>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="B175" s="35" t="s">
+        <v>245</v>
+      </c>
+      <c r="C175" s="35"/>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="B176" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="C176" s="35"/>
+    </row>
+    <row r="177" ht="28.8" spans="1:3">
+      <c r="A177" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="B177" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="C177" s="35"/>
+    </row>
+    <row r="178" ht="28.8" spans="1:3">
+      <c r="A178" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="B178" s="51" t="s">
+        <v>247</v>
+      </c>
+      <c r="C178" s="51"/>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B179" s="87" t="s">
+        <v>101</v>
+      </c>
+      <c r="C179" s="87" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180" s="56">
+        <v>1</v>
+      </c>
+      <c r="B180" s="56" t="s">
+        <v>248</v>
+      </c>
+      <c r="C180" s="56" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181" s="35">
+        <v>2</v>
+      </c>
+      <c r="B181" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="C181" s="35" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182" s="35">
+        <v>3</v>
+      </c>
+      <c r="B182" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="C182" s="35" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="183" ht="28.8" spans="1:3">
+      <c r="A183" s="35">
+        <v>4</v>
+      </c>
+      <c r="B183" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="C183" s="35" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
+      <c r="A186" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B186" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="C186" s="35"/>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="A187" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="B187" s="35" t="s">
+        <v>252</v>
+      </c>
+      <c r="C187" s="35"/>
+    </row>
+    <row r="188" spans="1:3">
+      <c r="A188" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="B188" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="C188" s="35"/>
+    </row>
+    <row r="189" ht="28.8" spans="1:3">
+      <c r="A189" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="B189" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="C189" s="35"/>
+    </row>
+    <row r="190" ht="28.8" spans="1:3">
+      <c r="A190" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="13" t="s">
+      <c r="B190" s="51" t="s">
+        <v>254</v>
+      </c>
+      <c r="C190" s="51"/>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B191" s="88" t="s">
+        <v>101</v>
+      </c>
+      <c r="C191" s="89" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
+      <c r="A192" s="56">
+        <v>1</v>
+      </c>
+      <c r="B192" s="56" t="s">
+        <v>236</v>
+      </c>
+      <c r="C192" s="90" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3">
+      <c r="A193" s="35">
+        <v>2</v>
+      </c>
+      <c r="B193" s="35" t="s">
+        <v>255</v>
+      </c>
+      <c r="C193" s="35" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194" s="35">
+        <v>3</v>
+      </c>
+      <c r="B194" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="C194" s="35" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="195" ht="28.8" spans="1:3">
+      <c r="A195" s="35">
+        <v>4</v>
+      </c>
+      <c r="B195" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="C195" s="35" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3">
+      <c r="A198" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B198" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="C198" s="35"/>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="A199" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B199" s="48" t="s">
+        <v>259</v>
+      </c>
+      <c r="C199" s="35"/>
+    </row>
+    <row r="200" ht="28.8" spans="1:3">
+      <c r="A200" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="B200" s="35" t="s">
+        <v>260</v>
+      </c>
+      <c r="C200" s="35"/>
+    </row>
+    <row r="201" ht="28.8" spans="1:3">
+      <c r="A201" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="B201" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="C201" s="35"/>
+    </row>
+    <row r="202" ht="28.8" spans="1:3">
+      <c r="A202" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="E8" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D9" s="13" t="s">
+      <c r="B202" s="50" t="s">
+        <v>261</v>
+      </c>
+      <c r="C202" s="51"/>
+    </row>
+    <row r="203" spans="1:3">
+      <c r="A203" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B203" s="87" t="s">
+        <v>101</v>
+      </c>
+      <c r="C203" s="91" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3">
+      <c r="A204" s="56">
+        <v>1</v>
+      </c>
+      <c r="B204" s="56" t="s">
+        <v>236</v>
+      </c>
+      <c r="C204" s="56" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3">
+      <c r="A205" s="35">
+        <v>2</v>
+      </c>
+      <c r="B205" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="C205" s="35" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3">
+      <c r="A206" s="35">
+        <v>3</v>
+      </c>
+      <c r="B206" s="35" t="s">
+        <v>262</v>
+      </c>
+      <c r="C206" s="35" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="207" ht="28.8" spans="1:3">
+      <c r="A207" s="35">
+        <v>4</v>
+      </c>
+      <c r="B207" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="C207" s="35" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3">
+      <c r="A210" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B210" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="C210" s="35"/>
+    </row>
+    <row r="211" spans="1:3">
+      <c r="A211" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B211" s="48" t="s">
+        <v>265</v>
+      </c>
+      <c r="C211" s="35"/>
+    </row>
+    <row r="212" ht="28.8" spans="1:3">
+      <c r="A212" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="B212" s="48" t="s">
+        <v>266</v>
+      </c>
+      <c r="C212" s="35"/>
+    </row>
+    <row r="213" ht="28.8" spans="1:3">
+      <c r="A213" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B213" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="C213" s="35"/>
+    </row>
+    <row r="214" spans="1:3">
+      <c r="A214" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D10" s="13" t="s">
+      <c r="B214" s="51" t="s">
+        <v>268</v>
+      </c>
+      <c r="C214" s="51"/>
+    </row>
+    <row r="215" spans="1:3">
+      <c r="A215" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B215" s="87" t="s">
+        <v>101</v>
+      </c>
+      <c r="C215" s="91" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="216" ht="28.8" spans="1:3">
+      <c r="A216" s="92">
+        <v>1</v>
+      </c>
+      <c r="B216" s="56" t="s">
+        <v>269</v>
+      </c>
+      <c r="C216" s="56" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="217" ht="28.8" spans="1:3">
+      <c r="A217" s="35">
+        <v>2</v>
+      </c>
+      <c r="B217" s="35" t="s">
+        <v>271</v>
+      </c>
+      <c r="C217" s="35" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="218" ht="28.8" spans="1:3">
+      <c r="A218" s="35">
+        <v>3</v>
+      </c>
+      <c r="B218" s="35" t="s">
+        <v>273</v>
+      </c>
+      <c r="C218" s="35" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3">
+      <c r="A221" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B221" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C221" s="35"/>
+    </row>
+    <row r="222" ht="28.8" spans="1:3">
+      <c r="A222" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B222" s="48" t="s">
+        <v>275</v>
+      </c>
+      <c r="C222" s="35"/>
+    </row>
+    <row r="223" spans="1:3">
+      <c r="A223" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="B223" s="35" t="s">
+        <v>276</v>
+      </c>
+      <c r="C223" s="35"/>
+    </row>
+    <row r="224" ht="28.8" spans="1:3">
+      <c r="A224" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="B224" s="35" t="s">
+        <v>277</v>
+      </c>
+      <c r="C224" s="35"/>
+    </row>
+    <row r="225" spans="1:3">
+      <c r="A225" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D11" s="13" t="s">
+      <c r="B225" s="51" t="s">
+        <v>278</v>
+      </c>
+      <c r="C225" s="51"/>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B226" s="87" t="s">
+        <v>101</v>
+      </c>
+      <c r="C226" s="91" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="227" ht="28.8" spans="1:3">
+      <c r="A227" s="56">
+        <v>1</v>
+      </c>
+      <c r="B227" s="56" t="s">
+        <v>279</v>
+      </c>
+      <c r="C227" s="56" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
+      <c r="A228" s="35">
+        <v>2</v>
+      </c>
+      <c r="B228" s="35" t="s">
+        <v>281</v>
+      </c>
+      <c r="C228" s="35" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="229" ht="28.8" spans="1:3">
+      <c r="A229" s="35">
+        <v>3</v>
+      </c>
+      <c r="B229" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="C229" s="35" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
+      <c r="A230" s="35">
+        <v>4</v>
+      </c>
+      <c r="B230" s="35" t="s">
+        <v>285</v>
+      </c>
+      <c r="C230" s="35" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="A233" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B233" s="35" t="s">
+        <v>287</v>
+      </c>
+      <c r="C233" s="35"/>
+    </row>
+    <row r="234" spans="1:3">
+      <c r="A234" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B234" s="48" t="s">
+        <v>288</v>
+      </c>
+      <c r="C234" s="35"/>
+    </row>
+    <row r="235" spans="1:3">
+      <c r="A235" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="B235" s="48" t="s">
+        <v>289</v>
+      </c>
+      <c r="C235" s="35"/>
+    </row>
+    <row r="236" ht="28.8" spans="1:3">
+      <c r="A236" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B236" s="48" t="s">
+        <v>290</v>
+      </c>
+      <c r="C236" s="35"/>
+    </row>
+    <row r="237" ht="28.8" spans="1:3">
+      <c r="A237" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D12" s="13" t="s">
+      <c r="B237" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="C237" s="51"/>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B238" s="87" t="s">
+        <v>101</v>
+      </c>
+      <c r="C238" s="91" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="239" ht="28.8" spans="1:3">
+      <c r="A239" s="56">
+        <v>1</v>
+      </c>
+      <c r="B239" s="56" t="s">
+        <v>292</v>
+      </c>
+      <c r="C239" s="56" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="240" ht="28.8" spans="1:3">
+      <c r="A240" s="35">
+        <v>2</v>
+      </c>
+      <c r="B240" s="35" t="s">
+        <v>294</v>
+      </c>
+      <c r="C240" s="35" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="241" ht="43.2" spans="1:3">
+      <c r="A241" s="35">
+        <v>3</v>
+      </c>
+      <c r="B241" s="35" t="s">
+        <v>296</v>
+      </c>
+      <c r="C241" s="35" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B244" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="C244" s="35"/>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="B245" s="35" t="s">
+        <v>298</v>
+      </c>
+      <c r="C245" s="35"/>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="B246" s="35" t="s">
+        <v>299</v>
+      </c>
+      <c r="C246" s="35"/>
+    </row>
+    <row r="247" ht="28.8" spans="1:3">
+      <c r="A247" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="B247" s="35" t="s">
+        <v>300</v>
+      </c>
+      <c r="C247" s="35"/>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="E12" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D13" s="13" t="s">
+      <c r="B248" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="C248" s="51"/>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B249" s="87" t="s">
+        <v>101</v>
+      </c>
+      <c r="C249" s="91" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="250" ht="28.8" spans="1:3">
+      <c r="A250" s="56">
+        <v>1</v>
+      </c>
+      <c r="B250" s="56" t="s">
+        <v>302</v>
+      </c>
+      <c r="C250" s="56" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="251" ht="28.8" spans="1:3">
+      <c r="A251" s="35">
+        <v>2</v>
+      </c>
+      <c r="B251" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="C251" s="35" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="252" ht="72" spans="1:3">
+      <c r="A252" s="35">
+        <v>3</v>
+      </c>
+      <c r="B252" s="35" t="s">
+        <v>306</v>
+      </c>
+      <c r="C252" s="35" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3">
+      <c r="A255" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B255" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="C255" s="35"/>
+    </row>
+    <row r="256" spans="1:3">
+      <c r="A256" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B256" s="48" t="s">
+        <v>308</v>
+      </c>
+      <c r="C256" s="35"/>
+    </row>
+    <row r="257" spans="1:3">
+      <c r="A257" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="B257" s="48" t="s">
+        <v>309</v>
+      </c>
+      <c r="C257" s="35"/>
+    </row>
+    <row r="258" ht="28.8" spans="1:3">
+      <c r="A258" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="B258" s="35" t="s">
+        <v>300</v>
+      </c>
+      <c r="C258" s="35"/>
+    </row>
+    <row r="259" spans="1:3">
+      <c r="A259" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="E13" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D14" s="13" t="s">
+      <c r="B259" s="51" t="s">
+        <v>310</v>
+      </c>
+      <c r="C259" s="51"/>
+    </row>
+    <row r="260" spans="1:3">
+      <c r="A260" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B260" s="87" t="s">
+        <v>101</v>
+      </c>
+      <c r="C260" s="91" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="261" ht="28.8" spans="1:3">
+      <c r="A261" s="56">
+        <v>1</v>
+      </c>
+      <c r="B261" s="56" t="s">
+        <v>302</v>
+      </c>
+      <c r="C261" s="56" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="262" ht="28.8" spans="1:3">
+      <c r="A262" s="35">
+        <v>2</v>
+      </c>
+      <c r="B262" s="35" t="s">
+        <v>312</v>
+      </c>
+      <c r="C262" s="35" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="263" ht="72" spans="1:3">
+      <c r="A263" s="35">
+        <v>3</v>
+      </c>
+      <c r="B263" s="35" t="s">
+        <v>306</v>
+      </c>
+      <c r="C263" s="35" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3">
+      <c r="A266" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B266" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C266" s="35"/>
+    </row>
+    <row r="267" spans="1:3">
+      <c r="A267" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B267" s="48" t="s">
+        <v>315</v>
+      </c>
+      <c r="C267" s="35"/>
+    </row>
+    <row r="268" spans="1:3">
+      <c r="A268" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="B268" s="48" t="s">
+        <v>316</v>
+      </c>
+      <c r="C268" s="35"/>
+    </row>
+    <row r="269" ht="28.8" spans="1:3">
+      <c r="A269" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B269" s="48" t="s">
+        <v>317</v>
+      </c>
+      <c r="C269" s="35"/>
+    </row>
+    <row r="270" spans="1:3">
+      <c r="A270" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D15" s="13" t="s">
+      <c r="B270" s="51" t="s">
+        <v>318</v>
+      </c>
+      <c r="C270" s="51"/>
+    </row>
+    <row r="271" spans="1:3">
+      <c r="A271" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B271" s="87" t="s">
+        <v>101</v>
+      </c>
+      <c r="C271" s="91" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="272" ht="28.8" spans="1:3">
+      <c r="A272" s="56">
+        <v>1</v>
+      </c>
+      <c r="B272" s="56" t="s">
+        <v>302</v>
+      </c>
+      <c r="C272" s="56" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="273" ht="28.8" spans="1:3">
+      <c r="A273" s="35">
+        <v>2</v>
+      </c>
+      <c r="B273" s="35" t="s">
+        <v>320</v>
+      </c>
+      <c r="C273" s="35" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="274" ht="43.2" spans="1:3">
+      <c r="A274" s="35">
+        <v>3</v>
+      </c>
+      <c r="B274" s="35" t="s">
+        <v>322</v>
+      </c>
+      <c r="C274" s="35" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3">
+      <c r="A277" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B277" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="C277" s="35"/>
+    </row>
+    <row r="278" spans="1:3">
+      <c r="A278" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B278" s="48" t="s">
+        <v>324</v>
+      </c>
+      <c r="C278" s="35"/>
+    </row>
+    <row r="279" spans="1:3">
+      <c r="A279" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="B279" s="35" t="s">
+        <v>325</v>
+      </c>
+      <c r="C279" s="35"/>
+    </row>
+    <row r="280" ht="28.8" spans="1:3">
+      <c r="A280" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="B280" s="35" t="s">
+        <v>317</v>
+      </c>
+      <c r="C280" s="35"/>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>191</v>
+      <c r="B281" s="51" t="s">
+        <v>326</v>
+      </c>
+      <c r="C281" s="51"/>
+      <c r="D281" s="30"/>
+    </row>
+    <row r="282" spans="1:3">
+      <c r="A282" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B282" s="59" t="s">
+        <v>101</v>
+      </c>
+      <c r="C282" s="60" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="283" ht="28.8" spans="1:3">
+      <c r="A283" s="56">
+        <v>1</v>
+      </c>
+      <c r="B283" s="56" t="s">
+        <v>302</v>
+      </c>
+      <c r="C283" s="56" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="284" ht="28.8" spans="1:3">
+      <c r="A284" s="35">
+        <v>2</v>
+      </c>
+      <c r="B284" s="35" t="s">
+        <v>327</v>
+      </c>
+      <c r="C284" s="35" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="285" ht="43.2" spans="1:3">
+      <c r="A285" s="35">
+        <v>3</v>
+      </c>
+      <c r="B285" s="35" t="s">
+        <v>322</v>
+      </c>
+      <c r="C285" s="35" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="40">
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="B155:C155"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -3535,27 +6809,27 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>330</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>193</v>
+        <v>331</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>194</v>
+        <v>332</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>195</v>
+        <v>333</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>196</v>
+        <v>334</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>93</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="8" t="s">
-        <v>197</v>
+        <v>336</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>63</v>
@@ -3564,18 +6838,18 @@
         <v>9</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>199</v>
+        <v>338</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="9" t="s">
-        <v>200</v>
+        <v>340</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>67</v>
@@ -3584,58 +6858,58 @@
         <v>9</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>201</v>
+        <v>341</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="9" t="s">
-        <v>202</v>
+        <v>342</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>203</v>
+        <v>343</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="9" t="s">
-        <v>204</v>
+        <v>344</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>205</v>
+        <v>345</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="9" t="s">
-        <v>206</v>
+        <v>346</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>66</v>
@@ -3644,18 +6918,18 @@
         <v>9</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>207</v>
+        <v>347</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="9" t="s">
-        <v>208</v>
+        <v>348</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>69</v>
@@ -3664,158 +6938,158 @@
         <v>9</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>209</v>
+        <v>349</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>117</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="9" t="s">
-        <v>210</v>
+        <v>351</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>211</v>
+        <v>352</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>212</v>
+        <v>353</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="9" t="s">
-        <v>213</v>
+        <v>354</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>211</v>
+        <v>352</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>214</v>
+        <v>355</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="9" t="s">
-        <v>215</v>
+        <v>356</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>211</v>
+        <v>352</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>216</v>
+        <v>357</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="9" t="s">
-        <v>217</v>
+        <v>358</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>211</v>
+        <v>352</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>218</v>
+        <v>359</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="9" t="s">
-        <v>219</v>
+        <v>360</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>138</v>
+        <v>188</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>211</v>
+        <v>352</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>220</v>
+        <v>361</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="9" t="s">
-        <v>221</v>
+        <v>362</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>142</v>
+        <v>196</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>211</v>
+        <v>352</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>222</v>
+        <v>363</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="9" t="s">
-        <v>223</v>
+        <v>364</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>147</v>
+        <v>213</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>211</v>
+        <v>352</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>224</v>
+        <v>365</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="9" t="s">
-        <v>225</v>
+        <v>366</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>79</v>
@@ -3824,18 +7098,18 @@
         <v>23</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>211</v>
+        <v>352</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>226</v>
+        <v>367</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="9" t="s">
-        <v>227</v>
+        <v>368</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>80</v>
@@ -3844,78 +7118,78 @@
         <v>39</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>228</v>
+        <v>369</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="9" t="s">
-        <v>229</v>
+        <v>370</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>157</v>
+        <v>244</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>39</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>230</v>
+        <v>371</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="9" t="s">
-        <v>231</v>
+        <v>372</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>161</v>
+        <v>251</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>39</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>232</v>
+        <v>373</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="9" t="s">
-        <v>233</v>
+        <v>374</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>165</v>
+        <v>258</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>234</v>
+        <v>375</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="9" t="s">
-        <v>235</v>
+        <v>376</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>83</v>
@@ -3924,18 +7198,18 @@
         <v>39</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>211</v>
+        <v>352</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>236</v>
+        <v>377</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="9" t="s">
-        <v>237</v>
+        <v>378</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>84</v>
@@ -3944,38 +7218,38 @@
         <v>39</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>238</v>
+        <v>379</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="9" t="s">
-        <v>239</v>
+        <v>380</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>176</v>
+        <v>287</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>39</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>240</v>
+        <v>381</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="9" t="s">
-        <v>241</v>
+        <v>382</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>86</v>
@@ -3984,18 +7258,18 @@
         <v>51</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>182</v>
+        <v>383</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="9" t="s">
-        <v>242</v>
+        <v>384</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>88</v>
@@ -4004,18 +7278,18 @@
         <v>51</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="9" t="s">
-        <v>243</v>
+        <v>386</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>89</v>
@@ -4024,18 +7298,18 @@
         <v>51</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>244</v>
+        <v>387</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="9" t="s">
-        <v>245</v>
+        <v>388</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>90</v>
@@ -4044,13 +7318,13 @@
         <v>51</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>246</v>
+        <v>389</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -4077,132 +7351,132 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>247</v>
+        <v>390</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>248</v>
+        <v>391</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>249</v>
+        <v>392</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>250</v>
+        <v>393</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>251</v>
+        <v>394</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>96</v>
+        <v>395</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>196</v>
+        <v>334</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>93</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" ht="57.6" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>252</v>
+        <v>396</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>253</v>
+        <v>397</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>255</v>
+        <v>399</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>256</v>
+        <v>401</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>257</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" ht="57.6" spans="1:8">
       <c r="A3" s="4" t="s">
-        <v>258</v>
+        <v>403</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>259</v>
+        <v>404</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>176</v>
+        <v>287</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>260</v>
+        <v>405</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>261</v>
+        <v>406</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>262</v>
+        <v>407</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>257</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" ht="72" spans="1:8">
       <c r="A4" s="6" t="s">
-        <v>263</v>
+        <v>408</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>264</v>
+        <v>409</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>80</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>265</v>
+        <v>410</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>266</v>
+        <v>411</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>267</v>
+        <v>412</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>268</v>
+        <v>413</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>257</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" ht="57.6" spans="1:8">
       <c r="A5" s="4" t="s">
-        <v>269</v>
+        <v>414</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>270</v>
+        <v>415</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>86</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>271</v>
+        <v>416</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>272</v>
+        <v>417</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>273</v>
+        <v>418</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>257</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
